--- a/app/pipeline_output/AKMEE/mapping_AKMEE_COMBINED.xlsx
+++ b/app/pipeline_output/AKMEE/mapping_AKMEE_COMBINED.xlsx
@@ -12,8 +12,8 @@
     <sheet name="For Review" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Field Mapping'!$A$1:$I$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'For Review'!$A$1:$I$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Field Mapping'!$A$1:$I$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'For Review'!$A$1:$I$72</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -47,7 +47,7 @@
       <color rgb="00FF0000"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -84,12 +84,6 @@
         <bgColor rgb="00FED8B1"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
-        <bgColor rgb="00F8CBAD"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -109,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -130,9 +124,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -500,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -579,12 +570,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER0</t>
+          <t>LOANPARAMETER2</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.0.value</t>
+          <t>loanAccount.loanParameters.2.value</t>
         </is>
       </c>
       <c r="F2" s="3" t="n">
@@ -624,12 +615,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER122</t>
+          <t>LOANPARAMETER3</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.122.value</t>
+          <t>loanAccount.loanParameters.3.value</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
@@ -939,12 +930,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER1</t>
+          <t>LOANPARAMETER10</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.1.value</t>
+          <t>loanAccount.loanParameters.10.value</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
@@ -1209,12 +1200,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER6</t>
+          <t>LOANPARAMETER17</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.6.value</t>
+          <t>loanAccount.loanParameters.17.value</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
@@ -1254,12 +1245,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME2</t>
+          <t>DOCUMENTNAME1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.1.document</t>
+          <t>loanAccount.loanDocuments.0.document</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
@@ -1569,12 +1560,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER69</t>
+          <t>LOANPARAMETER22</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.69.value</t>
+          <t>loanAccount.loanParameters.22.value</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
@@ -1704,12 +1695,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER6</t>
+          <t>LOANPARAMETER24</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.6.value</t>
+          <t>loanAccount.loanParameters.24.value</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
@@ -1929,12 +1920,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER30</t>
+          <t>LOANPARAMETER41</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.30.value</t>
+          <t>loanAccount.loanParameters.41.value</t>
         </is>
       </c>
       <c r="F32" s="4" t="n">
@@ -2064,12 +2055,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTID3</t>
+          <t>DOCUMENTID2</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.2.documentId</t>
+          <t>loanAccount.loanDocuments.1.documentId</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
@@ -2274,12 +2265,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>PanchardNumber</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>LeadFinancial</t>
+          <t>LeadProfile</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2289,25 +2280,25 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTCUSTOMERTYPE</t>
+          <t>PANNUMBER</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.customerType</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>0.93</v>
+          <t>customer.panNo</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>0.8144</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>llm_semantic</t>
+          <t>embedding</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>The field 'Type' in the context of 'LeadProfile' likely refers to the applicant's type, which corresponds to APPLICANTCUSTOMERTYPE.</t>
+          <t>Embedding: 'PanchardNumber' → 'PANNUMBER' sim=0.814</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2319,31 +2310,31 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>FatherSpouse</t>
+          <t>LoanTypeName</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>LeadProfile</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTFATHERNAME</t>
+          <t>APPLICANTLOANTYPE</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.fatherFirstName</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>0.85</v>
+          <t>loanAccount.loanType</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>0.95</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
@@ -2352,7 +2343,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>The field 'FatherSpouse' likely refers to the father's name, a common field, mapping to APPLICANTFATHERNAME, though the 'Spouse' part introduces some ambiguity.</t>
+          <t>The partner field 'LoanTypeName' clearly refers to the type of the loan, which corresponds to the internal key APPLICANTLOANTYPE.</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -2364,12 +2355,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>NoOfYearResiding</t>
+          <t>Remark</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>LeadAddress</t>
+          <t>LeadContact</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2379,16 +2370,16 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTINCURRENTADDRESSSINCE</t>
+          <t>APPLICANTPERSONALDISCUSSIONCOMMENTS</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.inCurrentAddressSince</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>0.93</v>
+          <t>loanAccount.customer.personalDiscussionComments</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>0.88</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
@@ -2397,7 +2388,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>The field 'NoOfYearResiding' is semantically equivalent to 'In Current Address Since', mapping to APPLICANTINCURRENTADDRESSSINCE.</t>
+          <t>The field 'Remark' semantically maps to a comments field like APPLICANTPERSONALDISCUSSIONCOMMENTS.</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2409,12 +2400,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>AreaOther</t>
+          <t>Address</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>LeadAddress</t>
+          <t>LeadReference</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2424,16 +2415,16 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTBUSINESSADDRESS2</t>
+          <t>BUSINESSVERIFICATIONADDRESS</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.locality</t>
+          <t>loanAccount.customer.verifications.0.address</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
@@ -2442,7 +2433,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>The field 'AreaOther' likely captures the locality or area of an address, which corresponds to APPLICANTBUSINESSADDRESS2.</t>
+          <t>The field 'Address' in the context of 'LeadReference' strongly matches BUSINESSVERIFICATIONADDRESS.</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -2454,12 +2445,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>OtherName</t>
+          <t>Relation</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>LeadDocument</t>
+          <t>LeadReference</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2469,25 +2460,25 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME4</t>
+          <t>BUSINESSVERIFICATIONENTERPRISERELATION1TYPE</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.3.document</t>
+          <t>loanAccount.customer.verifications.0.relationship</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>llm_pattern_document_name</t>
+          <t>llm_semantic</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Although the field name lacks a keyword, the category 'LeadDocument' strongly indicates this is a document name, mapping to DOCUMENTNAME.</t>
+          <t>The field 'Relation' in the context of 'LeadReference' strongly matches the relationship of a reference, which is BUSINESSVERIFICATIONENTERPRISERELATION1TYPE.</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2499,40 +2490,40 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>FileName</t>
+          <t>TypeName</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>LeadDocument</t>
+          <t>LeadProfile</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME5</t>
+          <t>APPLICANTCUSTOMERTYPE</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.4.document</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>0.9</v>
+          <t>loanAccount.customer.customerType</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>0.88</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>llm_pattern_document_name</t>
+          <t>llm_semantic</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>The field 'FileName' contains the document keyword 'File' and no locator keyword, matching the pattern for a document name.</t>
+          <t>The field 'TypeName' in the 'LeadProfile' context semantically matches APPLICANTCUSTOMERTYPE.</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2544,50 +2535,230 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>NoOfYearResiding</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>LeadAddress</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANTINCURRENTADDRESSSINCE</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.inCurrentAddressSince</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>The field 'NoOfYearResiding' semantically matches the concept of APPLICANTINCURRENTADDRESSSINCE.</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>OtherName</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>LeadDocument</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>DOCUMENTNAME3</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.loanDocuments.2.document</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>llm_pattern_document_name</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>The field 'OtherName' in a document context represents a document's name.</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>DocumentType</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>LeadDocument</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>DOCUMENT</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>DOCUMENTNAME4</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.loanDocuments.3.document</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>llm_pattern_document_name</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>The field 'DocumentType' refers to the name of a document and matches the document name pattern.</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>FileName</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>LeadDocument</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>DOCUMENT</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>DOCUMENTNAME5</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.loanDocuments.4.document</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>llm_pattern_document_name</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>The field 'FileName' refers to the name of a document and matches the document name pattern.</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
           <t>FilePath</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>LeadDocument</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>DOCUMENT</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>DOCUMENTID6</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>loanAccount.loanDocuments.5.documentId</t>
         </is>
       </c>
-      <c r="F46" s="3" t="n">
+      <c r="F50" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>llm_pattern_document_id</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>The field 'FilePath' contains the document keyword 'File' and the locator keyword 'Path', matching the pattern for a document identifier.</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>The field 'FilePath' refers to a document's location and matches the document ID pattern.</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I46"/>
+  <autoFilter ref="A1:I50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2598,7 +2769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2639,7 +2810,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-31 16:14:14</t>
+          <t>2026-04-06 15:20:04</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2821,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6">
@@ -2660,7 +2831,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
@@ -2670,7 +2841,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9">
@@ -2747,7 +2918,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -2767,17 +2938,17 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>llm_customerparameter</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
@@ -2797,7 +2968,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -2807,7 +2978,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -2824,7 +2995,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26">
@@ -2864,7 +3035,7 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31">
@@ -3117,55 +3288,65 @@
     <row r="52">
       <c r="C52" t="inlineStr">
         <is>
-          <t>... and 56 more</t>
+          <t>... and 51 more</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
+          <t>Mandatory Fields Missing:</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
           <t>Confidence Distribution:</t>
         </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>0.90-1.00</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>0.80-0.89</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>0.70-0.79</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>73</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="inlineStr">
         <is>
+          <t>0.90-1.00</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0.80-0.89</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0.70-0.79</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
           <t>0.00-0.69</t>
         </is>
       </c>
-      <c r="C58" t="n">
-        <v>3</v>
+      <c r="C61" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3179,7 +3360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -3348,12 +3529,12 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER0</t>
+          <t>LOANPARAMETER1</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.0.value</t>
+          <t>loanAccount.loanParameters.1.value</t>
         </is>
       </c>
       <c r="F4" s="9" t="n">
@@ -3393,12 +3574,12 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER2</t>
+          <t>LOANPARAMETER4</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.2.value</t>
+          <t>loanAccount.loanParameters.4.value</t>
         </is>
       </c>
       <c r="F5" s="9" t="n">
@@ -3438,12 +3619,12 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER3</t>
+          <t>LOANPARAMETER5</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.3.value</t>
+          <t>loanAccount.loanParameters.5.value</t>
         </is>
       </c>
       <c r="F6" s="9" t="n">
@@ -3483,12 +3664,12 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER43</t>
+          <t>LOANPARAMETER6</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.43.value</t>
+          <t>loanAccount.loanParameters.6.value</t>
         </is>
       </c>
       <c r="F7" s="9" t="n">
@@ -3528,12 +3709,12 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER44</t>
+          <t>LOANPARAMETER7</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.44.value</t>
+          <t>loanAccount.loanParameters.7.value</t>
         </is>
       </c>
       <c r="F8" s="9" t="n">
@@ -3573,12 +3754,12 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER116</t>
+          <t>LOANPARAMETER8</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.116.value</t>
+          <t>loanAccount.loanParameters.8.value</t>
         </is>
       </c>
       <c r="F9" s="9" t="n">
@@ -3618,12 +3799,12 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER125</t>
+          <t>LOANPARAMETER9</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.125.value</t>
+          <t>loanAccount.loanParameters.9.value</t>
         </is>
       </c>
       <c r="F10" s="9" t="n">
@@ -3708,12 +3889,12 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER15</t>
+          <t>LOANPARAMETER11</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.15.value</t>
+          <t>loanAccount.loanParameters.11.value</t>
         </is>
       </c>
       <c r="F12" s="9" t="n">
@@ -3753,12 +3934,12 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER79</t>
+          <t>LOANPARAMETER12</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.79.value</t>
+          <t>loanAccount.loanParameters.12.value</t>
         </is>
       </c>
       <c r="F13" s="9" t="n">
@@ -3798,12 +3979,12 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER19</t>
+          <t>LOANPARAMETER13</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.19.value</t>
+          <t>loanAccount.loanParameters.13.value</t>
         </is>
       </c>
       <c r="F14" s="9" t="n">
@@ -3843,12 +4024,12 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER20</t>
+          <t>LOANPARAMETER14</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.20.value</t>
+          <t>loanAccount.loanParameters.14.value</t>
         </is>
       </c>
       <c r="F15" s="9" t="n">
@@ -3888,12 +4069,12 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER33</t>
+          <t>LOANPARAMETER15</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.33.value</t>
+          <t>loanAccount.loanParameters.15.value</t>
         </is>
       </c>
       <c r="F16" s="9" t="n">
@@ -3933,12 +4114,12 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER23</t>
+          <t>LOANPARAMETER16</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.23.value</t>
+          <t>loanAccount.loanParameters.16.value</t>
         </is>
       </c>
       <c r="F17" s="9" t="n">
@@ -4023,12 +4204,12 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER84</t>
+          <t>LOANPARAMETER18</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.84.value</t>
+          <t>loanAccount.loanParameters.18.value</t>
         </is>
       </c>
       <c r="F19" s="9" t="n">
@@ -4068,12 +4249,12 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER85</t>
+          <t>LOANPARAMETER19</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.85.value</t>
+          <t>loanAccount.loanParameters.19.value</t>
         </is>
       </c>
       <c r="F20" s="9" t="n">
@@ -4113,12 +4294,12 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER86</t>
+          <t>LOANPARAMETER20</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.86.value</t>
+          <t>loanAccount.loanParameters.20.value</t>
         </is>
       </c>
       <c r="F21" s="9" t="n">
@@ -4158,12 +4339,12 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER83</t>
+          <t>LOANPARAMETER21</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.83.value</t>
+          <t>loanAccount.loanParameters.21.value</t>
         </is>
       </c>
       <c r="F22" s="9" t="n">
@@ -4383,12 +4564,12 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER30</t>
+          <t>LOANPARAMETER23</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.30.value</t>
+          <t>loanAccount.loanParameters.23.value</t>
         </is>
       </c>
       <c r="F27" s="9" t="n">
@@ -4428,12 +4609,12 @@
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER31</t>
+          <t>LOANPARAMETER25</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.31.value</t>
+          <t>loanAccount.loanParameters.25.value</t>
         </is>
       </c>
       <c r="F28" s="9" t="n">
@@ -4518,12 +4699,12 @@
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER33</t>
+          <t>LOANPARAMETER26</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.33.value</t>
+          <t>loanAccount.loanParameters.26.value</t>
         </is>
       </c>
       <c r="F30" s="9" t="n">
@@ -4563,12 +4744,12 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER34</t>
+          <t>LOANPARAMETER27</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.34.value</t>
+          <t>loanAccount.loanParameters.27.value</t>
         </is>
       </c>
       <c r="F31" s="9" t="n">
@@ -4608,12 +4789,12 @@
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER35</t>
+          <t>LOANPARAMETER28</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.35.value</t>
+          <t>loanAccount.loanParameters.28.value</t>
         </is>
       </c>
       <c r="F32" s="9" t="n">
@@ -4653,12 +4834,12 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER36</t>
+          <t>LOANPARAMETER29</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.36.value</t>
+          <t>loanAccount.loanParameters.29.value</t>
         </is>
       </c>
       <c r="F33" s="9" t="n">
@@ -4698,12 +4879,12 @@
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER55</t>
+          <t>LOANPARAMETER30</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.55.value</t>
+          <t>loanAccount.loanParameters.30.value</t>
         </is>
       </c>
       <c r="F34" s="9" t="n">
@@ -4743,12 +4924,12 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER56</t>
+          <t>LOANPARAMETER31</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.56.value</t>
+          <t>loanAccount.loanParameters.31.value</t>
         </is>
       </c>
       <c r="F35" s="9" t="n">
@@ -4788,12 +4969,12 @@
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER42</t>
+          <t>LOANPARAMETER32</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.42.value</t>
+          <t>loanAccount.loanParameters.32.value</t>
         </is>
       </c>
       <c r="F36" s="9" t="n">
@@ -4878,12 +5059,12 @@
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER57</t>
+          <t>LOANPARAMETER33</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.57.value</t>
+          <t>loanAccount.loanParameters.33.value</t>
         </is>
       </c>
       <c r="F38" s="9" t="n">
@@ -4968,12 +5149,12 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER58</t>
+          <t>LOANPARAMETER34</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.58.value</t>
+          <t>loanAccount.loanParameters.34.value</t>
         </is>
       </c>
       <c r="F40" s="9" t="n">
@@ -5013,12 +5194,12 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER62</t>
+          <t>LOANPARAMETER35</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.62.value</t>
+          <t>loanAccount.loanParameters.35.value</t>
         </is>
       </c>
       <c r="F41" s="9" t="n">
@@ -5058,12 +5239,12 @@
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER63</t>
+          <t>LOANPARAMETER36</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.63.value</t>
+          <t>loanAccount.loanParameters.36.value</t>
         </is>
       </c>
       <c r="F42" s="9" t="n">
@@ -5103,12 +5284,12 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER64</t>
+          <t>LOANPARAMETER37</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.64.value</t>
+          <t>loanAccount.loanParameters.37.value</t>
         </is>
       </c>
       <c r="F43" s="9" t="n">
@@ -5148,12 +5329,12 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER65</t>
+          <t>LOANPARAMETER38</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.65.value</t>
+          <t>loanAccount.loanParameters.38.value</t>
         </is>
       </c>
       <c r="F44" s="9" t="n">
@@ -5193,12 +5374,12 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER66</t>
+          <t>LOANPARAMETER39</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.66.value</t>
+          <t>loanAccount.loanParameters.39.value</t>
         </is>
       </c>
       <c r="F45" s="9" t="n">
@@ -5238,12 +5419,12 @@
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER67</t>
+          <t>LOANPARAMETER40</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.67.value</t>
+          <t>loanAccount.loanParameters.40.value</t>
         </is>
       </c>
       <c r="F46" s="9" t="n">
@@ -5463,12 +5644,12 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER40</t>
+          <t>LOANPARAMETER42</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.40.value</t>
+          <t>loanAccount.loanParameters.42.value</t>
         </is>
       </c>
       <c r="F51" s="9" t="n">
@@ -5508,12 +5689,12 @@
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>LOANPARAMETER41</t>
+          <t>LOANPARAMETER43</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.41.value</t>
+          <t>loanAccount.loanParameters.43.value</t>
         </is>
       </c>
       <c r="F52" s="9" t="n">
@@ -5628,40 +5809,40 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>LoanTypeName</t>
+          <t>AddressOR</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>LeadAddress</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>APPLICANTLOANTYPE</t>
+          <t>LOANAPPLICANTPARAM1</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanType</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.0.value</t>
         </is>
       </c>
       <c r="F55" s="9" t="n">
-        <v>0.7619</v>
+        <v>0.72</v>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>fuzzy</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>Fuzzy: 'LoanTypeName' ~ 'APPLICANTLOANTYPE' score=0.76</t>
+          <t>The field 'AddressOR' is a generic applicant attribute not present in the available keys.</t>
         </is>
       </c>
       <c r="I55" s="8" t="inlineStr">
@@ -5673,12 +5854,12 @@
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>PanchardNumber</t>
+          <t>AddressID</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>LeadProfile</t>
+          <t>LeadAddress</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
@@ -5688,25 +5869,25 @@
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>PANNUMBER</t>
+          <t>LOANAPPLICANTPARAM2</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>customer.panNo</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.1.value</t>
         </is>
       </c>
       <c r="F56" s="9" t="n">
-        <v>0.7826</v>
+        <v>0.72</v>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>fuzzy</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>Fuzzy: 'PanchardNumber' ~ 'PANNUMBER' score=0.78</t>
+          <t>The field 'AddressID' is a generic applicant attribute not present in the available keys.</t>
         </is>
       </c>
       <c r="I56" s="8" t="inlineStr">
@@ -5718,12 +5899,12 @@
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>AddressOR</t>
+          <t>RelationOther</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>LeadAddress</t>
+          <t>LeadReference</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
@@ -5733,25 +5914,25 @@
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>ADDRESSOFFPO</t>
+          <t>LOANAPPLICANTPARAM3</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.customer.enterprise.businessAddress1</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.2.value</t>
         </is>
       </c>
       <c r="F57" s="9" t="n">
-        <v>0.7619</v>
+        <v>0.72</v>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>fuzzy</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>Fuzzy: 'AddressOR' ~ 'ADDRESSOFFPO' score=0.76</t>
+          <t>The field 'RelationOther' is a generic applicant attribute not present in the available keys.</t>
         </is>
       </c>
       <c r="I57" s="8" t="inlineStr">
@@ -5763,12 +5944,12 @@
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>Remark</t>
+          <t>CurrentMarketValue</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>LeadContact</t>
+          <t>LeadLoan</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
@@ -5778,25 +5959,25 @@
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>REMARKS</t>
+          <t>LOANAPPLICANTPARAM4</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.fiRemarks</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.3.value</t>
         </is>
       </c>
       <c r="F58" s="9" t="n">
-        <v>0.7846</v>
+        <v>0.72</v>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>fuzzy</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>Fuzzy: 'Remark' ~ 'REMARKS' score=0.78</t>
+          <t>The field 'CurrentMarketValue' is a generic applicant attribute not present in the available keys.</t>
         </is>
       </c>
       <c r="I58" s="8" t="inlineStr">
@@ -5808,12 +5989,12 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>TenureType</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>LeadReference</t>
+          <t>LeadLoan</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
@@ -5823,25 +6004,25 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>ADDRESSOFFPO</t>
+          <t>LOANAPPLICANTPARAM5</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.customer.enterprise.businessAddress1</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.4.value</t>
         </is>
       </c>
       <c r="F59" s="9" t="n">
-        <v>0.7368</v>
+        <v>0.72</v>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>fuzzy</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>Fuzzy: 'Address' ~ 'ADDRESSOFFPO' score=0.74</t>
+          <t>The field 'TenureType' is a generic applicant attribute not present in the available keys.</t>
         </is>
       </c>
       <c r="I59" s="8" t="inlineStr">
@@ -5853,12 +6034,12 @@
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>Relation</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>LeadReference</t>
+          <t>LeadFinancial</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
@@ -5868,25 +6049,25 @@
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>RELIGION</t>
+          <t>LOANAPPLICANTPARAM6</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>customer.religion</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.5.value</t>
         </is>
       </c>
       <c r="F60" s="9" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>fuzzy</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>Fuzzy: 'Relation' ~ 'RELIGION' score=0.75</t>
+          <t>The field 'Type' is a generic applicant attribute not present in the available keys.</t>
         </is>
       </c>
       <c r="I60" s="8" t="inlineStr">
@@ -5898,12 +6079,12 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>Remark</t>
+          <t>FatherSpouse</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>LeadReference</t>
+          <t>LeadProfile</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
@@ -5913,25 +6094,25 @@
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>REMARKS</t>
+          <t>LOANAPPLICANTPARAM7</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.fiRemarks</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.6.value</t>
         </is>
       </c>
       <c r="F61" s="9" t="n">
-        <v>0.7846</v>
+        <v>0.72</v>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>fuzzy</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>Fuzzy: 'Remark' ~ 'REMARKS' score=0.78</t>
+          <t>The field 'FatherSpouse' is a generic applicant attribute not present in the available keys.</t>
         </is>
       </c>
       <c r="I61" s="8" t="inlineStr">
@@ -5943,27 +6124,27 @@
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>DocumentType</t>
+          <t>CibilGenerated</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>LeadDocument</t>
+          <t>LeadProfile</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME1</t>
+          <t>LOANAPPLICANTPARAM8</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.0.document</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.7.value</t>
         </is>
       </c>
       <c r="F62" s="9" t="n">
@@ -5971,12 +6152,12 @@
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>fuzzy</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>Fuzzy: 'DocumentType' ~ 'DOCUMENTNAME1' score=0.72</t>
+          <t>The field 'CibilGenerated' is a generic applicant attribute not present in the available keys.</t>
         </is>
       </c>
       <c r="I62" s="8" t="inlineStr">
@@ -5988,7 +6169,7 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>AddressID</t>
+          <t>IsPrimaryText</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
@@ -6003,25 +6184,25 @@
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>ADDRESSREMARKS</t>
+          <t>LOANAPPLICANTPARAM9</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.customer.customerAdditional.addressRemarks</t>
-        </is>
-      </c>
-      <c r="F63" s="10" t="n">
-        <v>0.6437</v>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.8.value</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="n">
+        <v>0.72</v>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>embedding</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>Embedding: 'AddressID' → 'ADDRESSREMARKS' sim=0.644</t>
+          <t>The field 'IsPrimaryText' is a generic applicant attribute not present in the available keys.</t>
         </is>
       </c>
       <c r="I63" s="8" t="inlineStr">
@@ -6033,12 +6214,12 @@
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>RelationOther</t>
+          <t>AreaOther</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>LeadReference</t>
+          <t>LeadAddress</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
@@ -6048,25 +6229,25 @@
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>RELATIONSHIPTOBUSINESS2</t>
+          <t>LOANAPPLICANTPARAM10</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>customer.enterpriseCustomerRelations.1.relationshipType</t>
-        </is>
-      </c>
-      <c r="F64" s="10" t="n">
-        <v>0.6324</v>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.9.value</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="n">
+        <v>0.72</v>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>embedding</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>Embedding: 'RelationOther' → 'RELATIONSHIPTOBUSINESS2' sim=0.632</t>
+          <t>The field 'AreaOther' is a generic applicant attribute not present in the available keys.</t>
         </is>
       </c>
       <c r="I64" s="8" t="inlineStr">
@@ -6078,12 +6259,12 @@
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>CurrentMarketValue</t>
+          <t>AreaPanchayatPopulation</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>LeadLoan</t>
+          <t>LeadAddress</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
@@ -6093,25 +6274,25 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>VEHICLECURRENTMARKETVALUE</t>
+          <t>LOANAPPLICANTPARAM11</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.vehicleLoanDetails.currentMarketValue</t>
-        </is>
-      </c>
-      <c r="F65" s="10" t="n">
-        <v>0.6709000000000001</v>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.10.value</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="n">
+        <v>0.72</v>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>embedding</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>Embedding: 'CurrentMarketValue' → 'VEHICLECURRENTMARKETVALUE' sim=0.745</t>
+          <t>The field 'AreaPanchayatPopulation' is a generic applicant attribute not present in the available keys.</t>
         </is>
       </c>
       <c r="I65" s="8" t="inlineStr">
@@ -6123,12 +6304,12 @@
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>TenureType</t>
+          <t>IsPrimary</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>LeadLoan</t>
+          <t>LeadContact</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
@@ -6138,25 +6319,25 @@
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>tenure</t>
+          <t>LOANAPPLICANTPARAM12</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>loanAccount.tenure</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.11.value</t>
         </is>
       </c>
       <c r="F66" s="9" t="n">
-        <v>0.7526</v>
+        <v>0.72</v>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>embedding</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>Embedding: 'TenureType' → 'tenure' sim=0.836</t>
+          <t>The field 'IsPrimary' is a generic applicant attribute not present in the available keys.</t>
         </is>
       </c>
       <c r="I66" s="8" t="inlineStr">
@@ -6168,12 +6349,12 @@
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>TypeName</t>
+          <t>ContactType</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>LeadProfile</t>
+          <t>LeadContact</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
@@ -6183,12 +6364,12 @@
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>LOANAPPLICANTPARAM13</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.12.value</t>
         </is>
       </c>
       <c r="F67" s="9" t="n">
@@ -6196,12 +6377,12 @@
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>llm_customerparameter</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>The field 'TypeName' is too generic to map to a specific excel key and falls back to a customer parameter.</t>
+          <t>The field 'ContactType' is a generic applicant attribute not present in the available keys.</t>
         </is>
       </c>
       <c r="I67" s="8" t="inlineStr">
@@ -6213,12 +6394,12 @@
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>CibilGenerated</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>LeadProfile</t>
+          <t>LeadContact</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
@@ -6228,12 +6409,12 @@
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>LOANAPPLICANTPARAM14</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.13.value</t>
         </is>
       </c>
       <c r="F68" s="9" t="n">
@@ -6241,12 +6422,12 @@
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>llm_customerparameter</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>The field 'CibilGenerated' appears to be a flag or status with no specific excel key, so it is mapped as a general customer parameter.</t>
+          <t>The field 'Value' is a generic applicant attribute not present in the available keys.</t>
         </is>
       </c>
       <c r="I68" s="8" t="inlineStr">
@@ -6258,12 +6439,12 @@
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>IsPrimaryText</t>
+          <t>Extension</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>LeadAddress</t>
+          <t>LeadContact</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
@@ -6273,12 +6454,12 @@
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>LOANAPPLICANTPARAM15</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.14.value</t>
         </is>
       </c>
       <c r="F69" s="9" t="n">
@@ -6286,12 +6467,12 @@
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>llm_customerparameter</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>The field 'IsPrimaryText' for an address does not have a specific excel key and is treated as a general customer parameter.</t>
+          <t>The field 'Extension' is a generic applicant attribute not present in the available keys.</t>
         </is>
       </c>
       <c r="I69" s="8" t="inlineStr">
@@ -6303,12 +6484,12 @@
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>AreaPanchayatPopulation</t>
+          <t>ReferenceID</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>LeadAddress</t>
+          <t>LeadReference</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
@@ -6318,12 +6499,12 @@
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>LOANAPPLICANTPARAM16</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.15.value</t>
         </is>
       </c>
       <c r="F70" s="9" t="n">
@@ -6331,12 +6512,12 @@
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>llm_customerparameter</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>No specific excel key exists for population data like 'AreaPanchayatPopulation', so it is mapped as a general customer parameter.</t>
+          <t>The field 'ReferenceID' is a generic applicant attribute not present in the available keys.</t>
         </is>
       </c>
       <c r="I70" s="8" t="inlineStr">
@@ -6348,12 +6529,12 @@
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>IsPrimary</t>
+          <t>ExShowroomPrice</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>LeadContact</t>
+          <t>LeadLoan</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
@@ -6363,12 +6544,12 @@
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>LOANAPPLICANTPARAM17</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.16.value</t>
         </is>
       </c>
       <c r="F71" s="9" t="n">
@@ -6376,12 +6557,12 @@
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>llm_customerparameter</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>The field 'IsPrimary' for contact information does not have a specific excel key and is treated as a general customer parameter.</t>
+          <t>The field 'ExShowroomPrice' is a generic applicant attribute not present in the available keys.</t>
         </is>
       </c>
       <c r="I71" s="8" t="inlineStr">
@@ -6393,12 +6574,12 @@
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>ContactType</t>
+          <t>Details</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>LeadContact</t>
+          <t>LeadBankDetails</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
@@ -6408,12 +6589,12 @@
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>LOANAPPLICANTPARAM18</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.17.value</t>
         </is>
       </c>
       <c r="F72" s="9" t="n">
@@ -6421,12 +6602,12 @@
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>llm_customerparameter</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>The field 'ContactType' describes the type of contact information, which doesn't map to a specific field in the denormalized schema, hence it's a customer parameter.</t>
+          <t>The field 'Details' is a generic applicant attribute not present in the available keys.</t>
         </is>
       </c>
       <c r="I72" s="8" t="inlineStr">
@@ -6435,233 +6616,8 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="8" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>LeadContact</t>
-        </is>
-      </c>
-      <c r="C73" s="8" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t>CUSTOMERPARAMETER</t>
-        </is>
-      </c>
-      <c r="E73" s="8" t="inlineStr">
-        <is>
-          <t>CUSTOMERPARAMETER</t>
-        </is>
-      </c>
-      <c r="F73" s="9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G73" s="8" t="inlineStr">
-        <is>
-          <t>llm_customerparameter</t>
-        </is>
-      </c>
-      <c r="H73" s="8" t="inlineStr">
-        <is>
-          <t>The field 'Value' for contact information is too generic without knowing the 'ContactType', so it is mapped as a customer parameter.</t>
-        </is>
-      </c>
-      <c r="I73" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="8" t="inlineStr">
-        <is>
-          <t>Extension</t>
-        </is>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>LeadContact</t>
-        </is>
-      </c>
-      <c r="C74" s="8" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D74" s="8" t="inlineStr">
-        <is>
-          <t>CUSTOMERPARAMETER</t>
-        </is>
-      </c>
-      <c r="E74" s="8" t="inlineStr">
-        <is>
-          <t>CUSTOMERPARAMETER</t>
-        </is>
-      </c>
-      <c r="F74" s="9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G74" s="8" t="inlineStr">
-        <is>
-          <t>llm_customerparameter</t>
-        </is>
-      </c>
-      <c r="H74" s="8" t="inlineStr">
-        <is>
-          <t>There is no specific excel key for a phone number extension, so 'Extension' is mapped as a customer parameter.</t>
-        </is>
-      </c>
-      <c r="I74" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="8" t="inlineStr">
-        <is>
-          <t>ReferenceID</t>
-        </is>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>LeadReference</t>
-        </is>
-      </c>
-      <c r="C75" s="8" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D75" s="8" t="inlineStr">
-        <is>
-          <t>CUSTOMERPARAMETER</t>
-        </is>
-      </c>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t>CUSTOMERPARAMETER</t>
-        </is>
-      </c>
-      <c r="F75" s="9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G75" s="8" t="inlineStr">
-        <is>
-          <t>llm_customerparameter</t>
-        </is>
-      </c>
-      <c r="H75" s="8" t="inlineStr">
-        <is>
-          <t>The field 'ReferenceID' does not correspond to any specific excel key and is mapped as a customer parameter.</t>
-        </is>
-      </c>
-      <c r="I75" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="8" t="inlineStr">
-        <is>
-          <t>ExShowroomPrice</t>
-        </is>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>LeadLoan</t>
-        </is>
-      </c>
-      <c r="C76" s="8" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t>CUSTOMERPARAMETER</t>
-        </is>
-      </c>
-      <c r="E76" s="8" t="inlineStr">
-        <is>
-          <t>CUSTOMERPARAMETER</t>
-        </is>
-      </c>
-      <c r="F76" s="9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G76" s="8" t="inlineStr">
-        <is>
-          <t>llm_customerparameter</t>
-        </is>
-      </c>
-      <c r="H76" s="8" t="inlineStr">
-        <is>
-          <t>No specific excel key exists for 'ExShowroomPrice' within the applicant scope, so it is mapped as a customer parameter.</t>
-        </is>
-      </c>
-      <c r="I76" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="8" t="inlineStr">
-        <is>
-          <t>Details</t>
-        </is>
-      </c>
-      <c r="B77" s="8" t="inlineStr">
-        <is>
-          <t>LeadBankDetails</t>
-        </is>
-      </c>
-      <c r="C77" s="8" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D77" s="8" t="inlineStr">
-        <is>
-          <t>CUSTOMERPARAMETER</t>
-        </is>
-      </c>
-      <c r="E77" s="8" t="inlineStr">
-        <is>
-          <t>CUSTOMERPARAMETER</t>
-        </is>
-      </c>
-      <c r="F77" s="9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G77" s="8" t="inlineStr">
-        <is>
-          <t>llm_customerparameter</t>
-        </is>
-      </c>
-      <c r="H77" s="8" t="inlineStr">
-        <is>
-          <t>The field 'Details' in the context of 'LeadBankDetails' is too generic to map to a specific excel key, so it is mapped as a customer parameter.</t>
-        </is>
-      </c>
-      <c r="I77" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I77"/>
+  <autoFilter ref="A1:I72"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>